--- a/output/Data and Chart Outputs/rhine_kaub_level_daily.xlsx
+++ b/output/Data and Chart Outputs/rhine_kaub_level_daily.xlsx
@@ -157,6 +157,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <areaChart>
@@ -333,7 +334,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
@@ -366,18 +367,32 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -724,7 +739,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -746,7 +760,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -761,7 +774,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>

--- a/output/Data and Chart Outputs/rhine_kaub_level_daily.xlsx
+++ b/output/Data and Chart Outputs/rhine_kaub_level_daily.xlsx
@@ -177,7 +177,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year chart'!$A$2:$A$366</f>
+              <f>'Water year chart'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -203,7 +203,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year chart'!$A$2:$A$366</f>
+              <f>'Water year chart'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -243,7 +243,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year chart'!$A$2:$A$366</f>
+              <f>'Water year chart'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -279,7 +279,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year chart'!$A$2:$A$366</f>
+              <f>'Water year chart'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -315,7 +315,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year chart'!$A$2:$A$366</f>
+              <f>'Water year chart'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -340,8 +340,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="30"/>
-        <tickMarkSkip val="30"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G366"/>
+  <dimension ref="A1:H366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -847,6 +847,11 @@
           <t>WY 2026/27</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Axis label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -872,6 +877,11 @@
       <c r="G2" t="n">
         <v>-5</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>01-Oct</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1554,6 +1564,11 @@
       <c r="F33" t="n">
         <v>294</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01-Nov</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2214,6 +2229,11 @@
       <c r="F63" t="n">
         <v>232</v>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>01-Dec</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2896,6 +2916,11 @@
       <c r="F94" t="n">
         <v>99</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>01-Jan</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3578,6 +3603,11 @@
       <c r="F125" t="n">
         <v>158</v>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>01-Feb</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4194,6 +4224,11 @@
       <c r="F153" t="n">
         <v>341</v>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01-Mar</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4876,6 +4911,11 @@
       <c r="F184" t="n">
         <v>140</v>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>01-Apr</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5536,6 +5576,11 @@
       <c r="F214" t="n">
         <v>117</v>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>01-May</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6218,6 +6263,11 @@
       <c r="F245" t="n">
         <v>111</v>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>01-Jun</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -6878,6 +6928,11 @@
       <c r="F275" t="n">
         <v>98</v>
       </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>01-Jul</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -7560,6 +7615,11 @@
       <c r="F306" t="n">
         <v>33</v>
       </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>01-Aug</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -8241,6 +8301,11 @@
       </c>
       <c r="F337" t="n">
         <v>64</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>01-Sep</t>
+        </is>
       </c>
     </row>
     <row r="338">

--- a/output/Data and Chart Outputs/rhine_kaub_level_daily.xlsx
+++ b/output/Data and Chart Outputs/rhine_kaub_level_daily.xlsx
@@ -338,6 +338,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
@@ -347,8 +359,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="683.8"/>
-          <min val="-37.8"/>
+          <max val="700"/>
+          <min val="-100"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -372,6 +384,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="100"/>
       </valAx>
       <spPr>
         <a:ln>

--- a/output/Data and Chart Outputs/rhine_kaub_level_daily.xlsx
+++ b/output/Data and Chart Outputs/rhine_kaub_level_daily.xlsx
@@ -152,7 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Rhine at Kaub - water year (Oct-Sep), data to 2026-10-01</a:t>
+              <a:t>Rhine at Kaub - water year (Oct-Sep), data to 2026-10-03</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -752,6 +752,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -773,6 +774,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -787,6 +789,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
@@ -888,7 +891,7 @@
         <v>210</v>
       </c>
       <c r="G2" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -917,6 +920,9 @@
       <c r="F3" t="n">
         <v>197</v>
       </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -938,6 +944,9 @@
       </c>
       <c r="F4" t="n">
         <v>180</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -8971,7 +8980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9772"/>
+  <dimension ref="A1:B9774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87151,7 +87160,23 @@
         <v>46296</v>
       </c>
       <c r="B9772" t="n">
-        <v>-5</v>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="9773">
+      <c r="A9773" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B9773" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9774">
+      <c r="A9774" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B9774" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/rhine_kaub_level_daily.xlsx
+++ b/output/Data and Chart Outputs/rhine_kaub_level_daily.xlsx
@@ -152,7 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Rhine at Kaub - water year (Oct-Sep), data to 2026-10-03</a:t>
+              <a:t>Rhine at Kaub - water year (Oct-Sep), data to 2026-10-08</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -946,7 +946,7 @@
         <v>180</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -970,6 +970,9 @@
       <c r="F5" t="n">
         <v>173</v>
       </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -992,6 +995,9 @@
       <c r="F6" t="n">
         <v>171</v>
       </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1014,6 +1020,9 @@
       <c r="F7" t="n">
         <v>167</v>
       </c>
+      <c r="G7" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1036,6 +1045,9 @@
       <c r="F8" t="n">
         <v>174</v>
       </c>
+      <c r="G8" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1057,6 +1069,9 @@
       </c>
       <c r="F9" t="n">
         <v>174</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="10">
@@ -8980,7 +8995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9774"/>
+  <dimension ref="A1:B9779"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87176,7 +87191,47 @@
         <v>46298</v>
       </c>
       <c r="B9774" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9775">
+      <c r="A9775" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B9775" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9776">
+      <c r="A9776" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B9776" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9777">
+      <c r="A9777" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B9777" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9778">
+      <c r="A9778" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B9778" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="9779">
+      <c r="A9779" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B9779" t="n">
+        <v>-2</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/rhine_kaub_level_daily.xlsx
+++ b/output/Data and Chart Outputs/rhine_kaub_level_daily.xlsx
@@ -152,7 +152,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Rhine at Kaub - water year (Oct-Sep), data to 2026-10-08</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Rhine at Kaub - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -264,7 +265,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -800,7 +801,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PEGELONLINE (German federal waterways administration)'s historische-zeitreihen archive: https://www.pegelonline.wsv.de/gast/historische-zeitreihen/prepare-download - a different endpoint from PEGELONLINE's regular /measurements.json API (that one only supports a 30-day window).</t>
+          <t>PEGELONLINE (German federal waterways administration)'s historische-zeitreihen archive: https://pegelonline.wsv.de/gast/download/prepare - a different endpoint from PEGELONLINE's regular /measurements.json API (that one only supports a 30-day window).</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1072,7 @@
         <v>174</v>
       </c>
       <c r="G9" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1095,6 +1096,9 @@
       <c r="F10" t="n">
         <v>170</v>
       </c>
+      <c r="G10" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1117,6 +1121,9 @@
       <c r="F11" t="n">
         <v>162</v>
       </c>
+      <c r="G11" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1139,6 +1146,9 @@
       <c r="F12" t="n">
         <v>152</v>
       </c>
+      <c r="G12" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1161,6 +1171,9 @@
       <c r="F13" t="n">
         <v>148</v>
       </c>
+      <c r="G13" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1183,6 +1196,9 @@
       <c r="F14" t="n">
         <v>140</v>
       </c>
+      <c r="G14" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1205,6 +1221,9 @@
       <c r="F15" t="n">
         <v>135</v>
       </c>
+      <c r="G15" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1227,6 +1246,9 @@
       <c r="F16" t="n">
         <v>129</v>
       </c>
+      <c r="G16" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1249,6 +1271,9 @@
       <c r="F17" t="n">
         <v>126</v>
       </c>
+      <c r="G17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1271,6 +1296,9 @@
       <c r="F18" t="n">
         <v>124</v>
       </c>
+      <c r="G18" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1293,6 +1321,9 @@
       <c r="F19" t="n">
         <v>123</v>
       </c>
+      <c r="G19" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1315,6 +1346,9 @@
       <c r="F20" t="n">
         <v>119</v>
       </c>
+      <c r="G20" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1337,6 +1371,9 @@
       <c r="F21" t="n">
         <v>116</v>
       </c>
+      <c r="G21" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1359,6 +1396,9 @@
       <c r="F22" t="n">
         <v>113</v>
       </c>
+      <c r="G22" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1381,6 +1421,9 @@
       <c r="F23" t="n">
         <v>119</v>
       </c>
+      <c r="G23" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1403,6 +1446,9 @@
       <c r="F24" t="n">
         <v>138</v>
       </c>
+      <c r="G24" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1425,6 +1471,9 @@
       <c r="F25" t="n">
         <v>193</v>
       </c>
+      <c r="G25" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1447,6 +1496,9 @@
       <c r="F26" t="n">
         <v>232</v>
       </c>
+      <c r="G26" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1469,6 +1521,9 @@
       <c r="F27" t="n">
         <v>242</v>
       </c>
+      <c r="G27" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1491,6 +1546,9 @@
       <c r="F28" t="n">
         <v>249</v>
       </c>
+      <c r="G28" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1512,6 +1570,9 @@
       </c>
       <c r="F29" t="n">
         <v>283</v>
+      </c>
+      <c r="G29" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="30">
@@ -8995,7 +9056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9779"/>
+  <dimension ref="A1:B9799"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87231,7 +87292,167 @@
         <v>46303</v>
       </c>
       <c r="B9779" t="n">
-        <v>-2</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9780">
+      <c r="A9780" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B9780" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9781">
+      <c r="A9781" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B9781" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9782">
+      <c r="A9782" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B9782" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9783">
+      <c r="A9783" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B9783" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9784">
+      <c r="A9784" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B9784" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9785">
+      <c r="A9785" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B9785" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9786">
+      <c r="A9786" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B9786" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9787">
+      <c r="A9787" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B9787" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9788">
+      <c r="A9788" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B9788" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9789">
+      <c r="A9789" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B9789" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9790">
+      <c r="A9790" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B9790" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9791">
+      <c r="A9791" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B9791" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9792">
+      <c r="A9792" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B9792" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9793">
+      <c r="A9793" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B9793" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9794">
+      <c r="A9794" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B9794" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9795">
+      <c r="A9795" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B9795" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9796">
+      <c r="A9796" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B9796" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9797">
+      <c r="A9797" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B9797" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9798">
+      <c r="A9798" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B9798" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9799">
+      <c r="A9799" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B9799" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
